--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_TRANCOSO_pgto_05-09-2026.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$H$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$128</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO AGO.26'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO AGO.26'!$A$4:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -838,7 +838,7 @@
       <c r="A22" s="4" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Os prêmios, vales, INSS e IRRF vieram do holerite de agosto emitido pela Betel Contabilidade. A linha DIFERENÇA fecha em zero para os cinco.</t>
+          <t>Os prêmios, vales, INSS e IRRF vieram do holerite de agosto emitido pela Betel Contabilidade. A linha DIFERENÇA fecha em zero para todos, exceto INIURLE, cujas horas extras foram corrigidas depois (16 h a 50% + 24 h a 100%).</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1284,84 +1284,99 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Adicional noturno</t>
+          <t>Adicional de hora extra 100%</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>20% sobre a hora normal, nas horas entre 22h e 5h.</t>
+          <t>100% sobre a hora normal (hora extra = salário-hora × 2).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Dias do mês para o salário-dia</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>30</v>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Salário-dia = salário base ÷ 30. Usado no feriado trabalhado.</t>
+          <t>20% sobre a hora normal, nas horas entre 22h e 5h.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Dias do mês para o salário-dia</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Salário-dia = salário base ÷ 30. Usado no feriado trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Multiplicador da comissão</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>TRANCOSO paga o dobro do valor apurado no InovaFarma.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>INSS / IRRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>a calcular</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>a calcular</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>IRRF</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>a calcular</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Calculado pela contabilidade após dedução do INSS e dependentes.</t>
         </is>
@@ -1372,7 +1387,7 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -1887,23 +1902,23 @@
         </is>
       </c>
       <c r="B7" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,B$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,B$4,'PONTO AGO.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="C7" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,C$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,C$4,'PONTO AGO.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="D7" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,D$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,D$4,'PONTO AGO.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="E7" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,E$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,E$4,'PONTO AGO.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="F7" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,F$4,'PONTO AGO.26'!$H$5:$H$13,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,F$4,'PONTO AGO.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="G7" s="20">
@@ -1923,23 +1938,23 @@
         </is>
       </c>
       <c r="B8" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,B$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,B$4,'PONTO AGO.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="C8" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,C$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,C$4,'PONTO AGO.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="D8" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,D$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,D$4,'PONTO AGO.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="E8" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,E$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,E$4,'PONTO AGO.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="F8" s="33">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$13,'PONTO AGO.26'!$A$5:$A$13,F$4,'PONTO AGO.26'!$H$5:$H$13,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$14,'PONTO AGO.26'!$A$5:$A$14,F$4,'PONTO AGO.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="G8" s="20">
@@ -1962,19 +1977,19 @@
         <v>0</v>
       </c>
       <c r="C9" s="33">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F6*PARÂMETROS!$B$20,2)</f>
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F6*PARÂMETROS!$B$21,2)</f>
         <v/>
       </c>
       <c r="D9" s="33">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F7*PARÂMETROS!$B$20,2)</f>
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F7*PARÂMETROS!$B$21,2)</f>
         <v/>
       </c>
       <c r="E9" s="33">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F8*PARÂMETROS!$B$20,2)</f>
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F8*PARÂMETROS!$B$21,2)</f>
         <v/>
       </c>
       <c r="F9" s="33">
-        <f>ROUND('BASE INOVAFARMA AGO.26'!F9*PARÂMETROS!$B$20,2)</f>
+        <f>ROUND('BASE INOVAFARMA AGO.26'!F9*PARÂMETROS!$B$21,2)</f>
         <v/>
       </c>
       <c r="G9" s="20">
@@ -6904,7 +6919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6991,7 +7006,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
@@ -7017,26 +7032,51 @@
       </c>
       <c r="I5" s="32" t="inlineStr">
         <is>
-          <t>40 horas extras normais em agosto/2026.</t>
+          <t>16 horas extras a 50% em agosto/2026.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="56" t="n"/>
-      <c r="B6" s="56" t="n"/>
-      <c r="C6" s="56" t="n"/>
-      <c r="D6" s="56" t="n"/>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>INIURLE</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Horas extras 100%</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
       <c r="E6" s="33">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A6,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="34" t="n"/>
+      <c r="F6" s="35">
+        <f>ROUND(E6/PARÂMETROS!$B$16*(1+PARÂMETROS!$B$18),4)</f>
+        <v/>
+      </c>
       <c r="G6" s="20">
         <f>ROUND(C6*F6,2)</f>
         <v/>
       </c>
-      <c r="H6" s="56" t="n"/>
-      <c r="I6" s="56" t="n"/>
+      <c r="H6" s="55" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>24 horas extras a 100% em agosto/2026 (antes lançadas como 40 h a 50%).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="56" t="n"/>
@@ -7158,96 +7198,113 @@
       <c r="I13" s="56" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="56" t="n"/>
+      <c r="B14" s="56" t="n"/>
+      <c r="C14" s="56" t="n"/>
+      <c r="D14" s="56" t="n"/>
+      <c r="E14" s="33">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$F$6,1,MATCH(A14,'HOLERITE AGO.26'!$B$4:$F$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="34" t="n"/>
+      <c r="G14" s="20">
+        <f>ROUND(C14*F14,2)</f>
+        <v/>
+      </c>
+      <c r="H14" s="56" t="n"/>
+      <c r="I14" s="56" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="20">
-        <f>SUM(G5:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
-        </is>
-      </c>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="20">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
+          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
           <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE AGO.26.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>OCORRÊNCIAS PARA A PRÓXIMA COMPETÊNCIA (SETEMBRO/2026) — NÃO ENTRAM NESTA FOLHA</t>
         </is>
       </c>
-      <c r="B21" s="28" t="n"/>
-      <c r="C21" s="28" t="n"/>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="28" t="n"/>
-      <c r="F21" s="28" t="n"/>
-      <c r="G21" s="28" t="n"/>
-      <c r="H21" s="28" t="n"/>
-      <c r="I21" s="28" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="28" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="28" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>TAMILES</t>
         </is>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B23" s="57" t="inlineStr">
         <is>
           <t>Atestado médico de 7 dias, entregue em 02/09/2026 — cobre de 02/09 a 08/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="9" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Cai na competência SETEMBRO/2026 (holerite pago em 05/10/2026), não nesta folha de agosto. Atestado de até 15 dias é abonado pela empresa: falta justificada, sem desconto de salário nem de DSR. A partir do 16º dia seria auxílio-doença pelo INSS. Anexar o atestado à pasta da funcionária.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I13"/>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="8">
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="B24:I24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="B22:I22"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
